--- a/Results/Result Summary.xlsx
+++ b/Results/Result Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Laboratory\tog-reusing-agents\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3068957F-59BA-490F-8607-7907F418E189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE2C26-677F-42CB-B673-79824234937D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="35">
   <si>
     <t xml:space="preserve">Design 1 </t>
   </si>
@@ -123,6 +123,24 @@
   </si>
   <si>
     <t>Design 3 pre</t>
+  </si>
+  <si>
+    <t>Design 3 finetune policy</t>
+  </si>
+  <si>
+    <t>Design 4 finetune policy</t>
+  </si>
+  <si>
+    <t>Design 4 policy finetuning</t>
+  </si>
+  <si>
+    <t>Design 3 policy finetuning</t>
+  </si>
+  <si>
+    <t>Design 4 policy tuning</t>
+  </si>
+  <si>
+    <t>Design 3 policy tuning</t>
   </si>
 </sst>
 </file>
@@ -428,7 +446,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
@@ -1207,6 +1225,112 @@
       <c r="K58">
         <f>_xlfn.STDEV.S(J48:J57)</f>
         <v>6.4669158027610044E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G62" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <v>-1.75</v>
+      </c>
+      <c r="J63">
+        <v>-1.081</v>
+      </c>
+    </row>
+    <row r="64" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <v>-2.0249999999999999</v>
+      </c>
+      <c r="J64">
+        <v>-1.081</v>
+      </c>
+    </row>
+    <row r="65" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G65">
+        <v>-1.7470000000000001</v>
+      </c>
+      <c r="J65">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="66" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <v>-2.0990000000000002</v>
+      </c>
+      <c r="J66">
+        <v>-1.099</v>
+      </c>
+    </row>
+    <row r="67" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <v>-1.8120000000000001</v>
+      </c>
+      <c r="J67">
+        <v>-1.0960000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <v>-1.833</v>
+      </c>
+      <c r="J68">
+        <v>-1.014</v>
+      </c>
+    </row>
+    <row r="69" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <v>-1.9990000000000001</v>
+      </c>
+      <c r="J69">
+        <v>-1.1619999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70">
+        <v>-2.0310000000000001</v>
+      </c>
+      <c r="J70">
+        <v>-1.0649999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G71">
+        <v>-1.94</v>
+      </c>
+      <c r="J71">
+        <v>-1.1120000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G72">
+        <v>-1.6919999999999999</v>
+      </c>
+      <c r="J72">
+        <v>-1.022</v>
+      </c>
+    </row>
+    <row r="73" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G73" s="1">
+        <f>AVERAGE(G62:G72)</f>
+        <v>-1.8928</v>
+      </c>
+      <c r="H73" s="1">
+        <f>_xlfn.STDEV.S(G62:G72)</f>
+        <v>0.14324633018374719</v>
+      </c>
+      <c r="J73" s="1">
+        <f>AVERAGE(J62:J72)</f>
+        <v>-1.0812000000000002</v>
+      </c>
+      <c r="K73" s="1">
+        <f>_xlfn.STDEV.S(J62:J72)</f>
+        <v>4.2554017958877206E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1344,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.42578125" customWidth="1"/>
@@ -1977,6 +2101,112 @@
       <c r="K57">
         <f>_xlfn.STDEV.S(J47:J56)</f>
         <v>9.0682596639781621E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J59" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G60">
+        <v>1.27</v>
+      </c>
+      <c r="J60">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="61" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G61">
+        <v>1.61</v>
+      </c>
+      <c r="J61">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="62" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G62">
+        <v>1.42</v>
+      </c>
+      <c r="J62">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="63" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <v>1.8</v>
+      </c>
+      <c r="J63">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="64" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <v>1.51</v>
+      </c>
+      <c r="J64">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="65" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G65">
+        <v>1.46</v>
+      </c>
+      <c r="J65">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="66" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <v>1.63</v>
+      </c>
+      <c r="J66">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="67" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <v>1.48</v>
+      </c>
+      <c r="J67">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="68" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <v>1.52</v>
+      </c>
+      <c r="J68">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="69" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <v>1.68</v>
+      </c>
+      <c r="J69">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="70" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70" s="1">
+        <f>AVERAGE(G60:G69)</f>
+        <v>1.5379999999999998</v>
+      </c>
+      <c r="H70" s="1">
+        <f>_xlfn.STDEV.S(G60:G69)</f>
+        <v>0.1486083592683953</v>
+      </c>
+      <c r="J70" s="1">
+        <f>AVERAGE(J60:J69)</f>
+        <v>1.073</v>
+      </c>
+      <c r="K70" s="1">
+        <f>_xlfn.STDEV.S(J60:J69)</f>
+        <v>0.10985343771488343</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +2220,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="21" max="21" width="15.140625" customWidth="1"/>
@@ -2991,22 +3221,114 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="62" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
+      <c r="G62">
+        <v>-1.47329909980297</v>
+      </c>
+      <c r="J62">
+        <v>0.46370011448860099</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <v>-1.8185989671945499</v>
+      </c>
+      <c r="J63">
+        <v>0.35610016375780101</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <v>-1.8167989188432601</v>
+      </c>
+      <c r="J64">
+        <v>0.42880012929439498</v>
+      </c>
+    </row>
+    <row r="65" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G65">
+        <v>-1.33659915506839</v>
+      </c>
+      <c r="J65">
+        <v>0.31160019576549502</v>
+      </c>
+    </row>
+    <row r="66" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <v>-1.3242991915345099</v>
+      </c>
+      <c r="J66">
+        <v>0.183500223457813</v>
+      </c>
+    </row>
+    <row r="67" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <v>-1.6374990037083601</v>
+      </c>
+      <c r="J67">
+        <v>0.27780020385980603</v>
+      </c>
+    </row>
+    <row r="68" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <v>-1.67809903085231</v>
+      </c>
+      <c r="J68">
+        <v>0.175300237834453</v>
+      </c>
+    </row>
+    <row r="69" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <v>-2.1505987736582699</v>
+      </c>
+      <c r="J69">
+        <v>0.28860019117593699</v>
+      </c>
+    </row>
+    <row r="70" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70">
+        <v>-1.70239898025989</v>
+      </c>
+      <c r="J70">
+        <v>0.24530021488666501</v>
+      </c>
+    </row>
+    <row r="71" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G71">
+        <v>-1.3699991139769501</v>
+      </c>
+      <c r="J71">
+        <v>-1.4099664390087099E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="7:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G72" s="1">
+        <f>AVERAGE(G62:G71)</f>
+        <v>-1.630819023489946</v>
+      </c>
+      <c r="H72" s="1">
+        <f>_xlfn.STDEV.S(G62:G71)</f>
+        <v>0.26263278520359412</v>
+      </c>
+      <c r="J72" s="1">
+        <f>AVERAGE(J62:J71)</f>
+        <v>0.27166020101308791</v>
+      </c>
+      <c r="K72" s="1">
+        <f>_xlfn.STDEV.S(J62:J71)</f>
+        <v>0.13745028697634759</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
